--- a/databases/PU Level C Book 1.xlsx
+++ b/databases/PU Level C Book 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\전한결\Documents\GitHub\Pattern_worksheet\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923D0795-2BB0-4B79-A7AD-55A156C87830}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06CDA63-2193-47CF-B27B-69D85B5208C2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2966,9 +2966,6 @@
     <t>이것은 네 우산이니?</t>
   </si>
   <si>
-    <t>이것은 네 자리니?</t>
-  </si>
-  <si>
     <t>이번이 네 처음이니?</t>
   </si>
   <si>
@@ -3102,6 +3099,10 @@
   </si>
   <si>
     <t>난 네가 날 도와줄 수 있는지 궁금해.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Korean/Question</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3522,7 +3523,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>963</v>
+        <v>1001</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
@@ -13568,7 +13569,7 @@
         <v>3</v>
       </c>
       <c r="E479" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.3">
@@ -13585,7 +13586,7 @@
         <v>3</v>
       </c>
       <c r="E480" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F480" t="s">
         <v>699</v>
@@ -13608,7 +13609,7 @@
         <v>3</v>
       </c>
       <c r="E481" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F481" t="s">
         <v>699</v>
@@ -13631,7 +13632,7 @@
         <v>4</v>
       </c>
       <c r="E482" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.3">
@@ -13648,7 +13649,7 @@
         <v>4</v>
       </c>
       <c r="E483" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F483" t="s">
         <v>702</v>
@@ -13671,7 +13672,7 @@
         <v>4</v>
       </c>
       <c r="E484" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F484" t="s">
         <v>702</v>
@@ -13694,7 +13695,7 @@
         <v>5</v>
       </c>
       <c r="E485" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.3">
@@ -13711,7 +13712,7 @@
         <v>5</v>
       </c>
       <c r="E486" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F486" t="s">
         <v>705</v>
@@ -13734,7 +13735,7 @@
         <v>5</v>
       </c>
       <c r="E487" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F487" t="s">
         <v>705</v>
@@ -13757,7 +13758,7 @@
         <v>6</v>
       </c>
       <c r="E488" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.3">
@@ -13774,7 +13775,7 @@
         <v>6</v>
       </c>
       <c r="E489" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F489" t="s">
         <v>708</v>
@@ -13797,7 +13798,7 @@
         <v>6</v>
       </c>
       <c r="E490" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F490" t="s">
         <v>708</v>
@@ -13820,7 +13821,7 @@
         <v>7</v>
       </c>
       <c r="E491" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.3">
@@ -13837,7 +13838,7 @@
         <v>7</v>
       </c>
       <c r="E492" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F492" t="s">
         <v>711</v>
@@ -13860,7 +13861,7 @@
         <v>7</v>
       </c>
       <c r="E493" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F493" t="s">
         <v>711</v>
@@ -13883,7 +13884,7 @@
         <v>8</v>
       </c>
       <c r="E494" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.3">
@@ -13900,7 +13901,7 @@
         <v>8</v>
       </c>
       <c r="E495" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F495" t="s">
         <v>714</v>
@@ -13923,7 +13924,7 @@
         <v>8</v>
       </c>
       <c r="E496" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="F496" t="s">
         <v>714</v>
@@ -13946,7 +13947,7 @@
         <v>9</v>
       </c>
       <c r="E497" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="498" spans="1:7" x14ac:dyDescent="0.3">
@@ -13963,7 +13964,7 @@
         <v>9</v>
       </c>
       <c r="E498" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F498" t="s">
         <v>717</v>
@@ -13986,7 +13987,7 @@
         <v>9</v>
       </c>
       <c r="E499" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F499" t="s">
         <v>717</v>
@@ -14009,7 +14010,7 @@
         <v>10</v>
       </c>
       <c r="E500" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="501" spans="1:7" x14ac:dyDescent="0.3">
@@ -14026,7 +14027,7 @@
         <v>10</v>
       </c>
       <c r="E501" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F501" t="s">
         <v>720</v>
@@ -14049,7 +14050,7 @@
         <v>10</v>
       </c>
       <c r="E502" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F502" t="s">
         <v>720</v>
@@ -14072,7 +14073,7 @@
         <v>11</v>
       </c>
       <c r="E503" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="504" spans="1:7" x14ac:dyDescent="0.3">
@@ -14089,7 +14090,7 @@
         <v>11</v>
       </c>
       <c r="E504" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F504" t="s">
         <v>723</v>
@@ -14112,7 +14113,7 @@
         <v>11</v>
       </c>
       <c r="E505" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F505" t="s">
         <v>723</v>
@@ -14135,7 +14136,7 @@
         <v>12</v>
       </c>
       <c r="E506" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="507" spans="1:7" x14ac:dyDescent="0.3">
@@ -14152,7 +14153,7 @@
         <v>12</v>
       </c>
       <c r="E507" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F507" t="s">
         <v>726</v>
@@ -14175,7 +14176,7 @@
         <v>12</v>
       </c>
       <c r="E508" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F508" t="s">
         <v>726</v>
@@ -14198,7 +14199,7 @@
         <v>1</v>
       </c>
       <c r="E509" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.3">
@@ -14215,7 +14216,7 @@
         <v>1</v>
       </c>
       <c r="E510" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F510" t="s">
         <v>730</v>
@@ -14238,7 +14239,7 @@
         <v>1</v>
       </c>
       <c r="E511" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F511" t="s">
         <v>730</v>
@@ -14261,7 +14262,7 @@
         <v>2</v>
       </c>
       <c r="E512" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.3">
@@ -14278,7 +14279,7 @@
         <v>2</v>
       </c>
       <c r="E513" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F513" t="s">
         <v>732</v>
@@ -14301,7 +14302,7 @@
         <v>2</v>
       </c>
       <c r="E514" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="F514" t="s">
         <v>732</v>
@@ -14324,7 +14325,7 @@
         <v>3</v>
       </c>
       <c r="E515" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.3">
@@ -14341,7 +14342,7 @@
         <v>3</v>
       </c>
       <c r="E516" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="F516" t="s">
         <v>735</v>
@@ -14364,7 +14365,7 @@
         <v>3</v>
       </c>
       <c r="E517" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="F517" t="s">
         <v>735</v>
@@ -14387,7 +14388,7 @@
         <v>4</v>
       </c>
       <c r="E518" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="519" spans="1:7" x14ac:dyDescent="0.3">
@@ -14404,7 +14405,7 @@
         <v>4</v>
       </c>
       <c r="E519" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F519" t="s">
         <v>738</v>
@@ -14427,7 +14428,7 @@
         <v>4</v>
       </c>
       <c r="E520" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F520" t="s">
         <v>738</v>
@@ -14450,7 +14451,7 @@
         <v>5</v>
       </c>
       <c r="E521" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="522" spans="1:7" x14ac:dyDescent="0.3">
@@ -14467,7 +14468,7 @@
         <v>5</v>
       </c>
       <c r="E522" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F522" t="s">
         <v>741</v>
@@ -14490,7 +14491,7 @@
         <v>5</v>
       </c>
       <c r="E523" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="F523" t="s">
         <v>741</v>
@@ -14513,7 +14514,7 @@
         <v>6</v>
       </c>
       <c r="E524" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.3">
@@ -14530,7 +14531,7 @@
         <v>6</v>
       </c>
       <c r="E525" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F525" t="s">
         <v>744</v>
@@ -14553,7 +14554,7 @@
         <v>6</v>
       </c>
       <c r="E526" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F526" t="s">
         <v>744</v>
@@ -14576,7 +14577,7 @@
         <v>7</v>
       </c>
       <c r="E527" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.3">
@@ -14593,7 +14594,7 @@
         <v>7</v>
       </c>
       <c r="E528" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="F528" t="s">
         <v>747</v>
@@ -14616,7 +14617,7 @@
         <v>7</v>
       </c>
       <c r="E529" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="F529" t="s">
         <v>747</v>
@@ -14639,7 +14640,7 @@
         <v>8</v>
       </c>
       <c r="E530" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.3">
@@ -14656,7 +14657,7 @@
         <v>8</v>
       </c>
       <c r="E531" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="F531" t="s">
         <v>750</v>
@@ -14679,7 +14680,7 @@
         <v>8</v>
       </c>
       <c r="E532" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="F532" t="s">
         <v>750</v>
@@ -14702,7 +14703,7 @@
         <v>9</v>
       </c>
       <c r="E533" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.3">
@@ -14719,7 +14720,7 @@
         <v>9</v>
       </c>
       <c r="E534" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F534" t="s">
         <v>753</v>
@@ -14742,7 +14743,7 @@
         <v>9</v>
       </c>
       <c r="E535" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F535" t="s">
         <v>753</v>
@@ -14765,7 +14766,7 @@
         <v>10</v>
       </c>
       <c r="E536" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.3">
@@ -14782,7 +14783,7 @@
         <v>10</v>
       </c>
       <c r="E537" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F537" t="s">
         <v>756</v>
@@ -14805,7 +14806,7 @@
         <v>10</v>
       </c>
       <c r="E538" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F538" t="s">
         <v>756</v>
@@ -14828,7 +14829,7 @@
         <v>11</v>
       </c>
       <c r="E539" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.3">
@@ -14845,7 +14846,7 @@
         <v>11</v>
       </c>
       <c r="E540" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F540" t="s">
         <v>759</v>
@@ -14868,7 +14869,7 @@
         <v>11</v>
       </c>
       <c r="E541" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F541" t="s">
         <v>759</v>
@@ -14891,7 +14892,7 @@
         <v>12</v>
       </c>
       <c r="E542" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.3">
@@ -14908,7 +14909,7 @@
         <v>12</v>
       </c>
       <c r="E543" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F543" t="s">
         <v>762</v>
@@ -14931,7 +14932,7 @@
         <v>12</v>
       </c>
       <c r="E544" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F544" t="s">
         <v>762</v>
@@ -15017,7 +15018,7 @@
         <v>2</v>
       </c>
       <c r="E548" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.3">
@@ -15034,7 +15035,7 @@
         <v>2</v>
       </c>
       <c r="E549" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F549" t="s">
         <v>770</v>
@@ -15057,7 +15058,7 @@
         <v>2</v>
       </c>
       <c r="E550" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F550" t="s">
         <v>770</v>
@@ -15206,7 +15207,7 @@
         <v>5</v>
       </c>
       <c r="E557" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="558" spans="1:7" x14ac:dyDescent="0.3">
@@ -15223,7 +15224,7 @@
         <v>5</v>
       </c>
       <c r="E558" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F558" t="s">
         <v>781</v>
@@ -15246,7 +15247,7 @@
         <v>5</v>
       </c>
       <c r="E559" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="F559" t="s">
         <v>781</v>
@@ -15269,7 +15270,7 @@
         <v>6</v>
       </c>
       <c r="E560" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="561" spans="1:7" x14ac:dyDescent="0.3">
@@ -15286,7 +15287,7 @@
         <v>6</v>
       </c>
       <c r="E561" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F561" t="s">
         <v>784</v>
@@ -15309,7 +15310,7 @@
         <v>6</v>
       </c>
       <c r="E562" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F562" t="s">
         <v>784</v>
@@ -15332,7 +15333,7 @@
         <v>7</v>
       </c>
       <c r="E563" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="564" spans="1:7" x14ac:dyDescent="0.3">
@@ -15349,7 +15350,7 @@
         <v>7</v>
       </c>
       <c r="E564" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F564" t="s">
         <v>787</v>
@@ -15372,7 +15373,7 @@
         <v>7</v>
       </c>
       <c r="E565" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F565" t="s">
         <v>787</v>
@@ -15395,7 +15396,7 @@
         <v>8</v>
       </c>
       <c r="E566" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="567" spans="1:7" x14ac:dyDescent="0.3">
@@ -15412,7 +15413,7 @@
         <v>8</v>
       </c>
       <c r="E567" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F567" t="s">
         <v>790</v>
@@ -15435,7 +15436,7 @@
         <v>8</v>
       </c>
       <c r="E568" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F568" t="s">
         <v>790</v>
@@ -15458,7 +15459,7 @@
         <v>9</v>
       </c>
       <c r="E569" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="570" spans="1:7" x14ac:dyDescent="0.3">
@@ -15475,7 +15476,7 @@
         <v>9</v>
       </c>
       <c r="E570" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F570" t="s">
         <v>793</v>
@@ -15498,7 +15499,7 @@
         <v>9</v>
       </c>
       <c r="E571" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F571" t="s">
         <v>793</v>
@@ -15521,7 +15522,7 @@
         <v>10</v>
       </c>
       <c r="E572" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="573" spans="1:7" x14ac:dyDescent="0.3">
@@ -15538,7 +15539,7 @@
         <v>10</v>
       </c>
       <c r="E573" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="F573" t="s">
         <v>796</v>
@@ -15561,7 +15562,7 @@
         <v>10</v>
       </c>
       <c r="E574" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="F574" t="s">
         <v>796</v>
@@ -16128,7 +16129,7 @@
         <v>7</v>
       </c>
       <c r="E601" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F601" t="s">
         <v>188</v>
@@ -16466,7 +16467,7 @@
         <v>1</v>
       </c>
       <c r="E617" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="618" spans="1:7" x14ac:dyDescent="0.3">
@@ -16483,7 +16484,7 @@
         <v>1</v>
       </c>
       <c r="E618" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F618" t="s">
         <v>201</v>
@@ -16506,7 +16507,7 @@
         <v>1</v>
       </c>
       <c r="E619" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F619" t="s">
         <v>201</v>
@@ -16592,7 +16593,7 @@
         <v>3</v>
       </c>
       <c r="E623" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="624" spans="1:7" x14ac:dyDescent="0.3">
@@ -16609,7 +16610,7 @@
         <v>3</v>
       </c>
       <c r="E624" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F624" t="s">
         <v>205</v>
@@ -16632,7 +16633,7 @@
         <v>3</v>
       </c>
       <c r="E625" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F625" t="s">
         <v>205</v>
@@ -16781,7 +16782,7 @@
         <v>6</v>
       </c>
       <c r="E632" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="633" spans="1:7" x14ac:dyDescent="0.3">
@@ -16798,7 +16799,7 @@
         <v>6</v>
       </c>
       <c r="E633" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F633" t="s">
         <v>211</v>
@@ -16821,7 +16822,7 @@
         <v>6</v>
       </c>
       <c r="E634" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F634" t="s">
         <v>211</v>
@@ -16844,7 +16845,7 @@
         <v>7</v>
       </c>
       <c r="E635" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.3">
@@ -16861,7 +16862,7 @@
         <v>7</v>
       </c>
       <c r="E636" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F636" t="s">
         <v>213</v>
@@ -16884,7 +16885,7 @@
         <v>7</v>
       </c>
       <c r="E637" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F637" t="s">
         <v>213</v>
@@ -16907,7 +16908,7 @@
         <v>8</v>
       </c>
       <c r="E638" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.3">
@@ -16924,7 +16925,7 @@
         <v>8</v>
       </c>
       <c r="E639" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F639" t="s">
         <v>215</v>
@@ -16947,7 +16948,7 @@
         <v>8</v>
       </c>
       <c r="E640" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F640" t="s">
         <v>215</v>
@@ -18608,7 +18609,7 @@
         <v>11</v>
       </c>
       <c r="E719" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="720" spans="1:7" x14ac:dyDescent="0.3">
@@ -18625,7 +18626,7 @@
         <v>11</v>
       </c>
       <c r="E720" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F720" t="s">
         <v>856</v>
@@ -18648,7 +18649,7 @@
         <v>11</v>
       </c>
       <c r="E721" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F721" t="s">
         <v>856</v>
